--- a/public/fixtures/sample-workbook.xlsx
+++ b/public/fixtures/sample-workbook.xlsx
@@ -298,6 +298,23 @@
         <v>13535000</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5">
+        <f>SUM(B4:B6)</f>
+        <v>28400000</v>
+      </c>
+      <c r="C7" s="5">
+        <f>SUM(C4:C6)</f>
+        <v>31625000</v>
+      </c>
+      <c r="D7" s="5">
+        <f>SUM(D4:D6)</f>
+        <v>60025000</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="3" t="s">
         <v>11</v>
@@ -320,23 +337,6 @@
         <v>10</v>
       </c>
       <c r="D10" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
-        <f>SUM(B4:B6)</f>
-        <v>28400000</v>
-      </c>
-      <c r="C7" s="5">
-        <f>SUM(C4:C6)</f>
-        <v>31625000</v>
-      </c>
-      <c r="D7" s="5">
-        <f>SUM(D4:D6)</f>
-        <v>60025000</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
